--- a/Table/UnitStatTable.xlsx
+++ b/Table/UnitStatTable.xlsx
@@ -213,35 +213,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>MaxDetectionRange-int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinDetectionRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxDetectionRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 탐색 범위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최소 탐색 범위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>MinxReactionSpeed-int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxDetectionRange-int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MinDetectionRange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxDetectionRange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 탐색 범위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최소 탐색 범위</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -660,10 +660,10 @@
         <v>47</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>41</v>
@@ -1021,24 +1021,24 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
